--- a/reports/jobs_2026-10-07.xlsx
+++ b/reports/jobs_2026-10-07.xlsx
@@ -520,17 +520,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Continental India</t>
+          <t>Arm India</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Tools &amp; Licensing Applications Engineer</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Electronic City,  Bengaluru, in</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -550,12 +550,12 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/continental/postings/744000154002299</t>
+          <t>https://careers.arm.com/job/bengaluru/tools-and-licensing-applications-engineer/33099/95071318624</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/continental</t>
+          <t>https://careers.arm.com/</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -567,12 +567,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer - Cloud: Azure</t>
+          <t>CA Industrial Trainee</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -582,14 +582,10 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>0-2 years</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bangalore </t>
-        </is>
-      </c>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -597,12 +593,12 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8258200?gh_jid=8258200</t>
+          <t>https://fractal.ai/en-US/Careers/job/Mumbai/CA-Industrial-Trainee_SR-46509-1</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -612,57 +608,61 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Agnikul Cosmos</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Careers Inquiries humancapital@agnikul.in</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>mailto:%20humancapital@agnikul.in</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>https://agnikul.in/careers</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Paytm</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Intern - Talent Acquisition</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Gurugram, Haryana</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/paytm/426a6834-1397-4e65-94af-69874c790805</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/paytm</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Agoda India</t>
+          <t>Agnikul Cosmos</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Chiang Mai 0 available jobs</t>
+          <t>Careers Inquiries humancapital@agnikul.in</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -675,11 +675,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai 0 available jobs Ok</t>
-        </is>
-      </c>
+      <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -687,12 +683,12 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/chiang-mai/</t>
+          <t>mailto:%20humancapital@agnikul.in</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/</t>
+          <t>https://agnikul.in/careers</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -709,7 +705,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Dubai 0 available jobs</t>
+          <t>Chiang Mai 0 available jobs</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -734,7 +730,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/dubai/</t>
+          <t>https://careersatagoda.com/location/chiang-mai/</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -756,7 +752,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Mumbai 0 available jobs</t>
+          <t>Dubai 0 available jobs</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -781,7 +777,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/mumbai/</t>
+          <t>https://careersatagoda.com/location/dubai/</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -803,7 +799,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Shanghai 1 available jobs</t>
+          <t>Mumbai 0 available jobs</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -828,7 +824,7 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/shanghai/</t>
+          <t>https://careersatagoda.com/location/mumbai/</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -850,7 +846,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Engineering &amp; Technology</t>
+          <t>Shanghai 1 available jobs</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -863,7 +859,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai 0 available jobs Ok</t>
+        </is>
+      </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -871,7 +871,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/department/technology/</t>
+          <t>https://careersatagoda.com/location/shanghai/</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Key Takeaways from Agoda’s AI Developer Report 2026 September 29, 2026 /</t>
+          <t>Engineering &amp; Technology</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/blog/tech/key-takeaways-from-agodas-ai-developer-report-2026/</t>
+          <t>https://careersatagoda.com/department/technology/</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>How Agoda is evolving engineering support with AI agents September 22, 2026 /</t>
+          <t>Key Takeaways from Agoda’s AI Developer Report 2026 September 29, 2026 /</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/blog/tech/how-agoda-is-evolving-engineering-support-with-ai-agents/</t>
+          <t>https://careersatagoda.com/blog/tech/key-takeaways-from-agodas-ai-developer-report-2026/</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Mumbai jobs</t>
+          <t>How Agoda is evolving engineering support with AI agents September 22, 2026 /</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -992,11 +992,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai jobs Yokohama jobs</t>
-        </is>
-      </c>
+      <c r="E12" s="4" t="inlineStr"/>
       <c r="F12" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -1004,7 +1000,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/mumbai-india/</t>
+          <t>https://careersatagoda.com/blog/tech/how-agoda-is-evolving-engineering-support-with-ai-agents/</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1026,12 +1022,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer Jobs</t>
+          <t>Mumbai jobs</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1039,7 +1035,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai jobs Yokohama jobs</t>
+        </is>
+      </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=back%20end</t>
+          <t>https://careersatagoda.com/location/mumbai-india/</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1069,12 +1069,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Developer Jobs</t>
+          <t>Backend Developer Jobs</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=Full%20Stack</t>
+          <t>https://careersatagoda.com/vacancies/?search=back%20end</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Jobs</t>
+          <t>Full Stack Developer Jobs</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=software%20engineer</t>
+          <t>https://careersatagoda.com/vacancies/?search=Full%20Stack</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1150,12 +1150,12 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Arm India</t>
+          <t>Agoda India</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Theorem Proving Engineer</t>
+          <t>Software Engineer Jobs</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/austin/theorem-proving-engineer/33099/97584421536</t>
+          <t>https://careersatagoda.com/vacancies/?search=software%20engineer</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/</t>
+          <t>https://careersatagoda.com/</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -1193,12 +1193,12 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Arm India</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Graphics Engineer</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/cambridge/graphics-engineer/33099/96521990288</t>
+          <t>https://www.atlassian.com/company/careers/engineering</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -1236,12 +1236,12 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Arm India</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Compiler Engineer (Machine Learning)</t>
+          <t>AI and Machine Learning</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/lund/compiler-engineer-machine-learning/33099/94847322016</t>
+          <t>https://www.atlassian.com/company/careers/engineering/ai</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -1279,12 +1279,12 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Chargebee</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Product Launch and price new features without waiting on engineering</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/engineering</t>
+          <t>https://www.chargebee.com/solutions/role/product/</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://www.chargebee.com/careers/</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -1322,17 +1322,17 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Chargebee</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>AI and Machine Learning</t>
+          <t>Growth Test offers, run promotions and lift conversion</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/engineering/ai</t>
+          <t>https://www.chargebee.com/solutions/role/growth/</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://www.chargebee.com/careers/</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
@@ -1365,17 +1365,17 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Chargebee</t>
+          <t>Continental India</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Product Launch and price new features without waiting on engineering</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1383,7 +1383,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Electronic City,  Bengaluru, in</t>
+        </is>
+      </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -1391,12 +1395,12 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/solutions/role/product/</t>
+          <t>https://api.smartrecruiters.com/v1/companies/continental/postings/744000154002299</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/continental</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -1408,12 +1412,12 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Chargebee</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Growth Test offers, run promotions and lift conversion</t>
+          <t>Implementation Engineer 2</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1426,7 +1430,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -1434,12 +1442,12 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/solutions/role/growth/</t>
+          <t>https://exotel.com/about-us/careers/#op-705944-implementation-engineer-2</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/careers/</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -1456,12 +1464,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Implementation Engineer 2</t>
+          <t>Integration &amp; Customisation Engineer - 1 (PHP + React.JS)</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1471,7 +1479,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>India Full-time</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1481,7 +1489,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705944-implementation-engineer-2</t>
+          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-1-php--reactjs</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1503,12 +1511,12 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer - 1 (PHP + React.JS)</t>
+          <t>Integration &amp; Customisation Engineer-3</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1518,7 +1526,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>India Full-time</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1528,7 +1536,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-1-php--reactjs</t>
+          <t>https://exotel.com/about-us/careers/#op-707788-integration--customisation-engineer3</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1550,7 +1558,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer-3</t>
+          <t>Integration &amp; Customization Engineer -1</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1565,7 +1573,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>India Full-time</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1575,7 +1583,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-707788-integration--customisation-engineer3</t>
+          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -1597,12 +1605,12 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customization Engineer -1</t>
+          <t>Integration and Customisation Engineer - 2 (PHP+React.JS)</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1610,11 +1618,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>India Full-time</t>
-        </is>
-      </c>
+      <c r="E26" s="4" t="inlineStr"/>
       <c r="F26" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -1622,7 +1626,7 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
+          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-phpreactjs</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -1644,12 +1648,12 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Integration and Customisation Engineer - 2 (PHP+React.JS)</t>
+          <t>Forward Deployed Engineer - 2</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1657,7 +1661,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -1665,7 +1673,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-phpreactjs</t>
+          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -1687,7 +1695,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - 2</t>
+          <t>Forward Deployed Engineer - 3</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1712,7 +1720,7 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
+          <t>https://exotel.com/about-us/careers/#op-706839-forward-deployed-engineer-3</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -1734,7 +1742,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - 3</t>
+          <t>Product Head, Voice AI</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1759,7 +1767,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-706839-forward-deployed-engineer-3</t>
+          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -1781,12 +1789,12 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Product Head, Voice AI</t>
+          <t>Software Developer - 3 (Golang/Java/Python)</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1806,7 +1814,7 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
+          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-golangjavapython</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -1828,12 +1836,12 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Software Developer - 3 (Golang/Java/Python)</t>
+          <t>Software Engineer - 2 (Voicebot)</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1853,7 +1861,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-golangjavapython</t>
+          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -1875,12 +1883,12 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 2 (Voicebot)</t>
+          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -1900,7 +1908,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
+          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -1917,17 +1925,17 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Fi Money</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
+          <t>DS/ML Intern</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1937,7 +1945,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -1947,12 +1955,12 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
+          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://jobs.lever.co/epifi</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
@@ -1964,17 +1972,17 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Fi Money</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>DS/ML Intern</t>
+          <t>AI Governance Arcitect</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -1982,11 +1990,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E34" s="4" t="inlineStr"/>
       <c r="F34" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -1994,12 +1998,12 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
+          <t>https://fractal.ai/en-US/Careers/job/New-Jersey/AI-Governance-Arcitect_SR-46463-1</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
@@ -2016,12 +2020,12 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>AI Governance Arcitect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2037,7 +2041,7 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/New-Jersey/AI-Governance-Arcitect_SR-46463-1</t>
+          <t>https://fractal.ai/en-US/Careers/job/New-Jersey/Data-Engineer_SR-46461-1</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2059,12 +2063,12 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineering Leader, Google COE</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -2080,7 +2084,7 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/New-Jersey/Data-Engineer_SR-46461-1</t>
+          <t>https://fractal.ai/en-US/Careers/job/California/Principal-Consultant-Decision-Scientist-4_SR-42734-1</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -2097,12 +2101,12 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>GitLab India</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Engineering Leader, Google COE</t>
+          <t>Software composition analysis</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2123,12 +2127,12 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/California/Principal-Consultant-Decision-Scientist-4_SR-42734-1</t>
+          <t>https://about.gitlab.com/solutions/supply-chain/</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://about.gitlab.com/jobs/all-jobs/</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
@@ -2140,17 +2144,17 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>GitLab India</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Software composition analysis</t>
+          <t>Internships and Programs</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2166,12 +2170,12 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/solutions/supply-chain/</t>
+          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/jobs/all-jobs/</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
@@ -2188,12 +2192,12 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Internships and Programs</t>
+          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2209,7 +2213,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
+          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -2226,17 +2230,17 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2244,7 +2248,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr"/>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru-VTP, India</t>
+        </is>
+      </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -2252,12 +2260,12 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://boards.greenhouse.io/groww</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
@@ -2274,7 +2282,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>YouTube &amp; Content - Internship</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2299,7 +2307,7 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4967486101</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -2316,17 +2324,17 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>HighRadius</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>YouTube &amp; Content - Internship</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2336,7 +2344,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru-VTP, India</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -2346,12 +2354,12 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4967486101</t>
+          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/groww</t>
+          <t>https://boards.greenhouse.io/highradius</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
@@ -2363,17 +2371,17 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>HighRadius</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Backend Engineer (Java / .NET)</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2383,7 +2391,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>Bangalore, in</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -2393,12 +2401,12 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000152347660</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/highradius</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
@@ -2415,12 +2423,12 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Backend Engineer (Java / .NET)</t>
+          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -2430,7 +2438,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, in</t>
+          <t>New Delhi, in</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -2440,7 +2448,7 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000152347660</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -2457,17 +2465,17 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>Lendingkart</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -2477,7 +2485,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>New Delhi, in</t>
+          <t>Bengaluru, in</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -2487,12 +2495,12 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
+          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://careers.smartrecruiters.com/lendingkart</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
@@ -2504,17 +2512,17 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Lendingkart</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Internship Opportunities</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -2522,11 +2530,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
+      <c r="E46" s="4" t="inlineStr"/>
       <c r="F46" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -2534,12 +2538,12 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
+          <t>https://careers.linkedin.com/pathways-programs/internships</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/lendingkart</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
@@ -2556,12 +2560,12 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Internship Opportunities</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -2577,7 +2581,7 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/pathways-programs/internships</t>
+          <t>https://careers.linkedin.com/Teams/Engineering</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -2594,12 +2598,12 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Cluster Head- Last mile - Chennai</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -2612,7 +2616,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr"/>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu</t>
+        </is>
+      </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -2620,12 +2628,12 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/Teams/Engineering</t>
+          <t>https://jobs.lever.co/meesho/c84e4b2c-653a-4cf8-abd9-e70d0c5e4cd8</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://jobs.lever.co/meesho</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -2642,7 +2650,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Cluster Head- Last mile - Chennai</t>
+          <t>Trainee - Recruitment Coordinator</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -2657,7 +2665,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Chennai, Tamil Nadu</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -2667,7 +2675,7 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/c84e4b2c-653a-4cf8-abd9-e70d0c5e4cd8</t>
+          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -2684,12 +2692,12 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>MoEngage</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Trainee - Recruitment Coordinator</t>
+          <t>For Developers</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -2702,11 +2710,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
+      <c r="E50" s="4" t="inlineStr"/>
       <c r="F50" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -2714,12 +2718,12 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
+          <t>https://www.moengage.com/role/for-developers/</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho</t>
+          <t>https://www.moengage.com/careers/</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
@@ -2731,12 +2735,12 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>MoEngage</t>
+          <t>MongoDB India</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>For Developers</t>
+          <t>Engineer 3 - Business Systems</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -2749,7 +2753,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr"/>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -2757,12 +2765,12 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/role/for-developers/</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/careers/</t>
+          <t>https://boards.greenhouse.io/mongodb</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
@@ -2774,17 +2782,17 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>MongoDB India</t>
+          <t>Mphasis</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Engineer 3 - Business Systems</t>
+          <t>TESTING</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -2792,11 +2800,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram</t>
-        </is>
-      </c>
+      <c r="E52" s="4" t="inlineStr"/>
       <c r="F52" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -2804,12 +2808,12 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
+          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/mongodb</t>
+          <t>https://careers.mphasis.com/</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
@@ -2821,17 +2825,17 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Mphasis</t>
+          <t>Okta India</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>TESTING</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -2839,7 +2843,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr"/>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, India</t>
+        </is>
+      </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -2847,12 +2855,12 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
+          <t>https://www.okta.com/company/careers/opportunity/8243101?gh_jid=8243101</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/</t>
+          <t>https://boards.greenhouse.io/okta</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
@@ -2864,17 +2872,17 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Okta India</t>
+          <t>PTC India</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Learn more about PTC internships</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -2882,11 +2890,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru, India</t>
-        </is>
-      </c>
+      <c r="E54" s="4" t="inlineStr"/>
       <c r="F54" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -2894,12 +2898,12 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>https://www.okta.com/company/careers/opportunity/8243101?gh_jid=8243101</t>
+          <t>https://www.ptc.com/en/careers/internships</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/okta</t>
+          <t>https://www.ptc.com/en/careers</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
@@ -2911,12 +2915,12 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>PTC India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Learn more about PTC internships</t>
+          <t>Intern-Talent Acquisition</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -2929,7 +2933,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr"/>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -2937,12 +2945,12 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers/internships</t>
+          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
@@ -2959,7 +2967,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Intern-Talent Acquisition</t>
+          <t>Internship - Talent Acquisition</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -2974,7 +2982,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -2984,7 +2992,7 @@
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
+          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -3006,7 +3014,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Internship - Talent Acquisition</t>
+          <t>Talent Acquisition Intern - Bangalore</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -3021,7 +3029,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -3031,7 +3039,7 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
+          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -3053,7 +3061,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Bangalore</t>
+          <t>Talent Acquisition Intern - Noida</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -3068,7 +3076,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -3078,7 +3086,7 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
+          <t>https://jobs.lever.co/paytm/36f0fe45-a771-4f97-aac1-0a9ca1d73f18</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -3095,17 +3103,17 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Publicis Sapient India</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Noida</t>
+          <t>Join our engineering talent community</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -3113,11 +3121,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>Noida, Uttar Pradesh</t>
-        </is>
-      </c>
+      <c r="E59" s="4" t="inlineStr"/>
       <c r="F59" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -3125,12 +3129,12 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/36f0fe45-a771-4f97-aac1-0a9ca1d73f18</t>
+          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://careers.publicissapient.com/</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
@@ -3142,17 +3146,17 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Publicis Sapient India</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Join our engineering talent community</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -3160,7 +3164,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr"/>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Indore, in</t>
+        </is>
+      </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -3168,12 +3176,12 @@
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>https://careers.publicissapient.com/</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
@@ -3190,12 +3198,12 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Laravel Developer</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -3215,7 +3223,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -3237,12 +3245,12 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Laravel Developer</t>
+          <t>Node.js Developer</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -3262,7 +3270,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -3279,17 +3287,17 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Ramco Systems</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Node.js Developer</t>
+          <t>Internships</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -3297,11 +3305,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>Indore, in</t>
-        </is>
-      </c>
+      <c r="E63" s="4" t="inlineStr"/>
       <c r="F63" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -3309,12 +3313,12 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
+          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://www.ramco.com/careers/</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
@@ -3326,17 +3330,17 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Ramco Systems</t>
+          <t>Razorpay</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Internships</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -3344,7 +3348,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr"/>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
@@ -3352,12 +3360,12 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
+          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4739199005</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/</t>
+          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
@@ -3369,17 +3377,17 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Razorpay</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>ENG Project/ Program - Intern</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -3389,7 +3397,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -3399,12 +3407,12 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4739199005</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
@@ -3421,12 +3429,12 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>ENG Project/ Program - Intern</t>
+          <t xml:space="preserve">Security Engineer - Identity and Access </t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -3436,7 +3444,7 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bangalore, India</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -3446,7 +3454,7 @@
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8220011?gh_jid=8220011</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -3468,7 +3476,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Security Engineer - Identity and Access </t>
+          <t>Software Engineer - Cloud: Azure</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -3478,12 +3486,12 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>0-2 years</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, India</t>
+          <t xml:space="preserve">Bangalore </t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -3493,7 +3501,7 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8220011?gh_jid=8220011</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8258200?gh_jid=8258200</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -4471,7 +4479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4559,19 +4567,19 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Vymo</t>
+          <t>Ather Energy</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://getvymo.com/careers/</t>
+          <t>https://www.atherenergy.com/careers</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
-  - navigating to "https://getvymo.com/careers/", waiting until "networkidle"
+  - navigating to "https://www.atherenergy.com/careers", waiting until "networkidle"
 </t>
         </is>
       </c>
@@ -4639,15 +4647,55 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Nykaa</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://www.nykaa.com/careers</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.nykaa.com/careers
+Call log:
+  - navigating to "https://www.nykaa.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Juspay</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://juspay.io/careers</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://juspay.io/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Darwinbox</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>https://darwinbox.com/careers</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4656,46 +4704,6 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Nykaa</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://www.nykaa.com/careers</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.nykaa.com/careers
-Call log:
-  - navigating to "https://www.nykaa.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Juspay</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>https://juspay.io/careers</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://juspay.io/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -4719,15 +4727,35 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>OYO</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://www.oyorooms.com/careers/</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.oyorooms.com/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Zomato</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>https://www.zomato.com/careers</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.zomato.com/careers
 Call log:
@@ -4736,18 +4764,18 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Swiggy</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>https://careers.swiggy.com/</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4756,18 +4784,18 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Coforge</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>https://www.coforge.com/careers</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.coforge.com/careers
 Call log:
@@ -4776,18 +4804,18 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Persistent Systems</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>https://www.persistent.com/careers/</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.persistent.com/careers/
 Call log:
@@ -4796,18 +4824,18 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Udaan</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>https://udaan.com/careers</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
